--- a/CPRD Raw Analysis/Results/Output_costs_Raw-Adjusted.xlsx
+++ b/CPRD Raw Analysis/Results/Output_costs_Raw-Adjusted.xlsx
@@ -414,7 +414,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1159.06</v>
+        <v>1101.01</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -423,28 +423,28 @@
         <v>14098.5</v>
       </c>
       <c r="D2">
-        <v>944.09</v>
+        <v>923.77</v>
       </c>
       <c r="E2">
-        <v>924</v>
+        <v>882</v>
       </c>
       <c r="F2">
-        <v>536.09</v>
+        <v>481.2</v>
       </c>
       <c r="G2">
-        <v>1512</v>
+        <v>1454.75</v>
       </c>
       <c r="H2">
-        <v>22558</v>
+        <v>13627</v>
       </c>
       <c r="I2">
-        <v>6.285836802527252</v>
+        <v>7.91341107049772</v>
       </c>
       <c r="J2">
-        <v>1146.739325151528</v>
+        <v>1085.498621470716</v>
       </c>
       <c r="K2">
-        <v>1171.380674848472</v>
+        <v>1116.521378529284</v>
       </c>
     </row>
   </sheetData>
@@ -516,7 +516,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1168.96</v>
+        <v>1116.61</v>
       </c>
       <c r="B2">
         <v>6</v>
@@ -525,28 +525,28 @@
         <v>14098.5</v>
       </c>
       <c r="D2">
-        <v>941.99</v>
+        <v>914.42</v>
       </c>
       <c r="E2">
-        <v>934.38</v>
+        <v>883.16</v>
       </c>
       <c r="F2">
-        <v>546</v>
+        <v>504</v>
       </c>
       <c r="G2">
-        <v>1519.81</v>
+        <v>1470</v>
       </c>
       <c r="H2">
-        <v>22367</v>
+        <v>13971</v>
       </c>
       <c r="I2">
-        <v>6.298576718360181</v>
+        <v>7.736276261601566</v>
       </c>
       <c r="J2">
-        <v>1156.614348378034</v>
+        <v>1101.445863329706</v>
       </c>
       <c r="K2">
-        <v>1181.305651621966</v>
+        <v>1131.774136670294</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_costs_Raw-Adjusted.xlsx
+++ b/CPRD Raw Analysis/Results/Output_costs_Raw-Adjusted.xlsx
@@ -414,37 +414,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1101.01</v>
+        <v>925.67</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>14098.5</v>
+        <v>14096</v>
       </c>
       <c r="D2">
-        <v>923.77</v>
+        <v>904.0599999999999</v>
       </c>
       <c r="E2">
-        <v>882</v>
+        <v>683.98</v>
       </c>
       <c r="F2">
-        <v>481.2</v>
+        <v>299.04</v>
       </c>
       <c r="G2">
-        <v>1454.75</v>
+        <v>1260</v>
       </c>
       <c r="H2">
         <v>13627</v>
       </c>
       <c r="I2">
-        <v>7.91341107049772</v>
+        <v>7.744566734570475</v>
       </c>
       <c r="J2">
-        <v>1085.498621470716</v>
+        <v>910.4895796863022</v>
       </c>
       <c r="K2">
-        <v>1116.521378529284</v>
+        <v>940.8504203136977</v>
       </c>
     </row>
   </sheetData>
@@ -516,37 +516,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1116.61</v>
+        <v>958.59</v>
       </c>
       <c r="B2">
         <v>6</v>
       </c>
       <c r="C2">
-        <v>14098.5</v>
+        <v>14096</v>
       </c>
       <c r="D2">
-        <v>914.42</v>
+        <v>902.6799999999999</v>
       </c>
       <c r="E2">
-        <v>883.16</v>
+        <v>714</v>
       </c>
       <c r="F2">
-        <v>504</v>
+        <v>336</v>
       </c>
       <c r="G2">
-        <v>1470</v>
+        <v>1293.36</v>
       </c>
       <c r="H2">
-        <v>13971</v>
+        <v>13159</v>
       </c>
       <c r="I2">
-        <v>7.736276261601566</v>
+        <v>7.869051303496055</v>
       </c>
       <c r="J2">
-        <v>1101.445863329706</v>
+        <v>943.1655240038803</v>
       </c>
       <c r="K2">
-        <v>1131.774136670294</v>
+        <v>974.0144759961198</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_costs_Raw-Adjusted.xlsx
+++ b/CPRD Raw Analysis/Results/Output_costs_Raw-Adjusted.xlsx
@@ -414,7 +414,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>925.67</v>
+        <v>1086.33</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -423,28 +423,28 @@
         <v>14096</v>
       </c>
       <c r="D2">
-        <v>904.0599999999999</v>
+        <v>930.0599999999999</v>
       </c>
       <c r="E2">
-        <v>683.98</v>
+        <v>848.37</v>
       </c>
       <c r="F2">
-        <v>299.04</v>
+        <v>464.28</v>
       </c>
       <c r="G2">
-        <v>1260</v>
+        <v>1428</v>
       </c>
       <c r="H2">
-        <v>13627</v>
+        <v>15088</v>
       </c>
       <c r="I2">
-        <v>7.744566734570475</v>
+        <v>7.571730172132114</v>
       </c>
       <c r="J2">
-        <v>910.4895796863022</v>
+        <v>1071.488490893558</v>
       </c>
       <c r="K2">
-        <v>940.8504203136977</v>
+        <v>1101.171509106442</v>
       </c>
     </row>
   </sheetData>
@@ -516,37 +516,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>958.59</v>
+        <v>1098.93</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C2">
         <v>14096</v>
       </c>
       <c r="D2">
-        <v>902.6799999999999</v>
+        <v>928.01</v>
       </c>
       <c r="E2">
-        <v>714</v>
+        <v>862.14</v>
       </c>
       <c r="F2">
-        <v>336</v>
+        <v>482.9</v>
       </c>
       <c r="G2">
-        <v>1293.36</v>
+        <v>1436.37</v>
       </c>
       <c r="H2">
-        <v>13159</v>
+        <v>14915</v>
       </c>
       <c r="I2">
-        <v>7.869051303496055</v>
+        <v>7.598730243541569</v>
       </c>
       <c r="J2">
-        <v>943.1655240038803</v>
+        <v>1084.035553618287</v>
       </c>
       <c r="K2">
-        <v>974.0144759961198</v>
+        <v>1113.824446381713</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_costs_Raw-Adjusted.xlsx
+++ b/CPRD Raw Analysis/Results/Output_costs_Raw-Adjusted.xlsx
@@ -414,37 +414,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1086.33</v>
+        <v>54617.7</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="C2">
-        <v>14096</v>
+        <v>10265367.94</v>
       </c>
       <c r="D2">
-        <v>930.0599999999999</v>
+        <v>173110.34</v>
       </c>
       <c r="E2">
-        <v>848.37</v>
+        <v>16722.87</v>
       </c>
       <c r="F2">
-        <v>464.28</v>
+        <v>4914.81</v>
       </c>
       <c r="G2">
-        <v>1428</v>
+        <v>48977.22</v>
       </c>
       <c r="H2">
-        <v>15088</v>
+        <v>15040</v>
       </c>
       <c r="I2">
-        <v>7.571730172132114</v>
+        <v>1411.559181472828</v>
       </c>
       <c r="J2">
-        <v>1071.488490893558</v>
+        <v>51850.87216348648</v>
       </c>
       <c r="K2">
-        <v>1101.171509106442</v>
+        <v>57384.52783651352</v>
       </c>
     </row>
   </sheetData>
@@ -516,37 +516,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1098.93</v>
+        <v>1412.07</v>
       </c>
       <c r="B2">
-        <v>12</v>
+        <v>0.95</v>
       </c>
       <c r="C2">
-        <v>14096</v>
+        <v>19934</v>
       </c>
       <c r="D2">
-        <v>928.01</v>
+        <v>1280.43</v>
       </c>
       <c r="E2">
-        <v>862.14</v>
+        <v>1081.8</v>
       </c>
       <c r="F2">
-        <v>482.9</v>
+        <v>588</v>
       </c>
       <c r="G2">
-        <v>1436.37</v>
+        <v>1841.12</v>
       </c>
       <c r="H2">
-        <v>14915</v>
+        <v>14934</v>
       </c>
       <c r="I2">
-        <v>7.598730243541569</v>
+        <v>10.47774361921209</v>
       </c>
       <c r="J2">
-        <v>1084.035553618287</v>
+        <v>1391.532335229701</v>
       </c>
       <c r="K2">
-        <v>1113.824446381713</v>
+        <v>1432.607664770299</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_costs_Raw-Adjusted.xlsx
+++ b/CPRD Raw Analysis/Results/Output_costs_Raw-Adjusted.xlsx
@@ -414,37 +414,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>54617.7</v>
+        <v>1086.33</v>
       </c>
       <c r="B2">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>10265367.94</v>
+        <v>14096</v>
       </c>
       <c r="D2">
-        <v>173110.34</v>
+        <v>930.0599999999999</v>
       </c>
       <c r="E2">
-        <v>16722.87</v>
+        <v>848.37</v>
       </c>
       <c r="F2">
-        <v>4914.81</v>
+        <v>464.28</v>
       </c>
       <c r="G2">
-        <v>48977.22</v>
+        <v>1428</v>
       </c>
       <c r="H2">
-        <v>15040</v>
+        <v>15088</v>
       </c>
       <c r="I2">
-        <v>1411.559181472828</v>
+        <v>7.571730172132114</v>
       </c>
       <c r="J2">
-        <v>51850.87216348648</v>
+        <v>1071.488490893558</v>
       </c>
       <c r="K2">
-        <v>57384.52783651352</v>
+        <v>1101.171509106442</v>
       </c>
     </row>
   </sheetData>
@@ -516,37 +516,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1412.07</v>
+        <v>1098.93</v>
       </c>
       <c r="B2">
-        <v>0.95</v>
+        <v>12</v>
       </c>
       <c r="C2">
-        <v>19934</v>
+        <v>14096</v>
       </c>
       <c r="D2">
-        <v>1280.43</v>
+        <v>928.01</v>
       </c>
       <c r="E2">
-        <v>1081.8</v>
+        <v>862.14</v>
       </c>
       <c r="F2">
-        <v>588</v>
+        <v>482.9</v>
       </c>
       <c r="G2">
-        <v>1841.12</v>
+        <v>1436.37</v>
       </c>
       <c r="H2">
-        <v>14934</v>
+        <v>14915</v>
       </c>
       <c r="I2">
-        <v>10.47774361921209</v>
+        <v>7.598730243541569</v>
       </c>
       <c r="J2">
-        <v>1391.532335229701</v>
+        <v>1084.035553618287</v>
       </c>
       <c r="K2">
-        <v>1432.607664770299</v>
+        <v>1113.824446381713</v>
       </c>
     </row>
   </sheetData>
